--- a/src/cubegenpy/templates/UVIS_data_definition_v0.5.xlsx
+++ b/src/cubegenpy/templates/UVIS_data_definition_v0.5.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-04T20:01:56+00:00</t>
+          <t>2026-09-04T21:19:43+00:00</t>
         </is>
       </c>
     </row>
@@ -3703,7 +3703,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4760,6 +4760,37 @@
       <c r="G33" t="inlineStr">
         <is>
           <t>GEOMETRY_ONLY (science arrays are placeholders) or CALIBRATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>NT_RULE</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>computed:nt_rule</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>NT policy; see cubegenpy.subsampling</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4932,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Beginning, middle and end at minimum; finer for long smeared products (rule TBD).</t>
+          <t>Beginning, middle and end at minimum; finer for long smeared products. The rule is a policy set per product -- see cubegenpy.subsampling and the NT_RULE header keyword, which records the policy that chose it. The value itself is the last axis of every backplane TDIM; it is not repeated in a keyword.</t>
         </is>
       </c>
     </row>
